--- a/data/trans_bre/IP18A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Habitat-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,32</t>
+          <t>-4,76; 3,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 6,85</t>
+          <t>-5,66; 6,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 7,86</t>
+          <t>-4,8; 7,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,89</t>
+          <t>0,0; 28,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,03; 123,85</t>
+          <t>-72,28; 152,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 107,82</t>
+          <t>-44,8; 93,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 130,05</t>
+          <t>-43,33; 116,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,89</t>
+          <t>-3,07; 5,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 2,55</t>
+          <t>-6,6; 2,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 3,21</t>
+          <t>-5,29; 2,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 9,97</t>
+          <t>-8,19; 10,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 129,57</t>
+          <t>-39,78; 144,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 43,53</t>
+          <t>-56,97; 37,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,24; 48,7</t>
+          <t>-47,97; 48,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,1; 284,85</t>
+          <t>-76,35; 271,44</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 6,52</t>
+          <t>-5,26; 6,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 4,97</t>
+          <t>-5,42; 5,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 6,29</t>
+          <t>-4,25; 6,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 16,59</t>
+          <t>-1,38; 14,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 92,14</t>
+          <t>-40,75; 83,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,71; 78,61</t>
+          <t>-48,7; 94,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 121,07</t>
+          <t>-41,35; 123,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 4,56</t>
+          <t>-6,8; 4,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 6,77</t>
+          <t>-4,72; 6,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,38</t>
+          <t>-3,24; 8,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 17,27</t>
+          <t>-5,0; 16,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 48,13</t>
+          <t>-44,53; 47,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 70,77</t>
+          <t>-32,08; 74,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 116,22</t>
+          <t>-28,78; 131,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,63</t>
+          <t>-2,49; 2,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,54</t>
+          <t>-2,85; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,37</t>
+          <t>-1,94; 3,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 9,46</t>
+          <t>-1,13; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 40,07</t>
+          <t>-25,11; 40,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 28,98</t>
+          <t>-25,08; 30,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 45,02</t>
+          <t>-19,34; 47,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 420,35</t>
+          <t>-28,56; 410,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Habitat-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,57</t>
+          <t>-4,63; 3,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 6,58</t>
+          <t>-5,68; 6,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,28</t>
+          <t>-5,89; 6,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,58</t>
+          <t>0,0; 26,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,28; 152,36</t>
+          <t>-72,7; 173,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 93,48</t>
+          <t>-44,45; 85,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 116,47</t>
+          <t>-51,29; 116,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,05</t>
+          <t>-3,06; 5,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 2,33</t>
+          <t>-6,19; 2,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 2,99</t>
+          <t>-5,75; 2,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 10,16</t>
+          <t>-7,61; 11,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 144,5</t>
+          <t>-38,96; 130,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,97; 37,16</t>
+          <t>-56,81; 46,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,97; 48,88</t>
+          <t>-52,13; 46,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,35; 271,44</t>
+          <t>-76,56; 303,88</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 6,22</t>
+          <t>-5,23; 6,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 5,08</t>
+          <t>-5,48; 4,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 6,32</t>
+          <t>-4,42; 6,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 14,75</t>
+          <t>-1,35; 14,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,75; 83,24</t>
+          <t>-40,26; 89,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 94,0</t>
+          <t>-49,01; 76,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,35; 123,99</t>
+          <t>-40,53; 117,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 4,44</t>
+          <t>-6,47; 4,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 6,63</t>
+          <t>-4,64; 6,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 8,35</t>
+          <t>-3,82; 7,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 16,54</t>
+          <t>-4,4; 17,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,53; 47,23</t>
+          <t>-42,52; 52,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 74,58</t>
+          <t>-31,72; 72,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 131,15</t>
+          <t>-32,88; 105,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,84</t>
+          <t>-2,42; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,66</t>
+          <t>-2,63; 2,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,47</t>
+          <t>-1,99; 3,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 9,21</t>
+          <t>-1,09; 8,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 40,48</t>
+          <t>-24,33; 37,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 30,85</t>
+          <t>-22,89; 29,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 47,03</t>
+          <t>-19,62; 42,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 410,84</t>
+          <t>-31,08; 390,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,52</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 3,68</t>
+          <t>-4,65; 3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 6,49</t>
+          <t>-5,76; 6,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 6,96</t>
+          <t>-5,45; 7,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,98</t>
+          <t>0,0; 27,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,7; 173,3</t>
+          <t>-73,03; 123,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,45; 85,47</t>
+          <t>-47,08; 107,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,29; 116,91</t>
+          <t>-45,11; 130,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 5,12</t>
+          <t>-3,28; 4,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 2,71</t>
+          <t>-6,29; 2,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,83</t>
+          <t>-5,42; 3,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 11,58</t>
+          <t>-8,35; 11,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 130,49</t>
+          <t>-44,09; 129,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,81; 46,13</t>
+          <t>-56,16; 43,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,13; 46,4</t>
+          <t>-51,24; 48,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,56; 303,88</t>
+          <t>-78,3; 380,47</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>275,61%</t>
+          <t>347,08%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 6,24</t>
+          <t>-5,15; 6,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 4,93</t>
+          <t>-5,91; 4,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 6,58</t>
+          <t>-4,68; 6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 14,87</t>
+          <t>-0,95; 17,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 89,87</t>
+          <t>-40,72; 92,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 76,15</t>
+          <t>-47,71; 78,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 117,54</t>
+          <t>-44,5; 121,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>124,2%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 4,91</t>
+          <t>-6,38; 4,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 6,87</t>
+          <t>-4,22; 6,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 7,2</t>
+          <t>-3,06; 7,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 17,69</t>
+          <t>-3,87; 18,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,52; 52,24</t>
+          <t>-43,32; 48,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 72,54</t>
+          <t>-29,73; 70,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 105,27</t>
+          <t>-28,14; 116,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,8</t>
+          <t>-2,41; 2,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,58</t>
+          <t>-2,91; 2,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,19</t>
+          <t>-1,71; 3,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 8,81</t>
+          <t>-1,1; 9,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 37,78</t>
+          <t>-26,3; 40,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 29,32</t>
+          <t>-25,77; 28,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 42,47</t>
+          <t>-17,06; 45,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 390,59</t>
+          <t>-29,5; 457,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,48</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-12,96%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>-0.5959382930450057</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.3585447913025286</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8078711361884636</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.480131399209442</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1296198262500038</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.03539350157435563</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.08773845971523798</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +650,166 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,65; 3,32</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,76; 6,85</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 7,86</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 27,97</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-73,03; 123,85</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-47,08; 107,82</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-45,11; 130,05</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.653210893985287</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.760632645257537</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.452739121197165</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7303366001036333</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4707813697844841</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.4510940744744359</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.319786540440463</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.845708641250511</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.864637471882485</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>27.96886792473153</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.238493279071853</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.078217073307659</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.30045550017181</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-21,05%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-14,3%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,28; 4,89</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,29; 2,55</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,42; 3,21</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-8,35; 11,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-44,09; 129,57</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-56,16; 43,53</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-51,24; 48,7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-78,3; 380,47</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.012993848426352</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.862412495370504</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.253799628869545</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.8861901056294641</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1754326223699669</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2104635557635528</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1429608683304709</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1229182236545986</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,43</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-3,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>347,08%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.275640551298198</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.29182648196679</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.420298078548821</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-8.345239479610672</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4408911885213091</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5615813486466394</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5123788879429954</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7829839863946433</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,15; 6,52</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,91; 4,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,68; 6,29</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,95; 17,73</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-40,72; 92,14</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-47,71; 78,61</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-44,5; 121,07</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.888296020380826</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.54931197566735</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.213418147109159</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>11.61266697545162</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.295734884694055</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.4352561495552023</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4869709030547598</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>3.804692533199443</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +817,289 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,65</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-8,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>124,2%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.8052487535051875</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.3406498336074162</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9087194600652451</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.431287091183126</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.08124573882588161</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.03774682432162201</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.1107813173100167</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>3.470768698916036</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,38; 4,56</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,22; 6,77</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,06; 7,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,87; 18,13</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-43,32; 48,13</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-29,73; 70,77</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-28,14; 116,22</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.146397431442243</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.913307205647976</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.680833564000313</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.9531291922526217</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4072267909348989</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4770700086750372</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4449773381696723</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.523609719028128</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.972302500929744</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.288270550322343</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>17.7290870718914</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.9214474213180088</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7860888943599665</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.210672321198614</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.078331788233394</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9638015965383773</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.340345488848222</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.650989013636766</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.0864877299217725</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.08129576783999191</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2650322990096697</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1.242000558758515</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.380370473231229</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.222035767814325</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.056088062428402</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.872102457016053</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4332058244195538</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2973298140778995</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2813700595690775</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.561530264372428</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.768784878019719</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.384874968684533</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>18.13181865099014</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4812692727460888</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7077154671539938</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.162164392071056</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,42</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,99%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,41; 2,63</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,91; 2,54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 3,37</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,1; 9,85</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-26,3; 40,07</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-25,77; 28,98</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-17,06; 45,02</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-29,5; 457,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.1865206089009711</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.199116853063841</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.6549749645332823</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>3.422645378771939</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.02230335883997556</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.01989680966884111</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.07482316246469671</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.9159230222830604</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.412795972206937</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.914181561081118</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.709905473812558</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.098157685879488</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2629950415362667</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2576581532216187</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.170592426250566</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2950211345951732</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.628549223601048</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.535898748553755</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.374837299810923</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.852401927746843</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.4006877900348612</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2898031412045661</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.4502107027156207</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>4.570886511026245</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1107,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
